--- a/paper/data/merapi_literature_P.xlsx
+++ b/paper/data/merapi_literature_P.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7F24011-EECF-4D24-AED9-F8A12A47E3D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7BF9EEF-1A5C-4A57-9811-8178746CEC9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5920" yWindow="4760" windowWidth="28800" windowHeight="15380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4910" yWindow="3180" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pressure" sheetId="1" r:id="rId1"/>
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="84">
   <si>
     <t>(Preece et al., 2014)</t>
   </si>
@@ -327,9 +327,6 @@
   </si>
   <si>
     <t>Post-hoc</t>
-  </si>
-  <si>
-    <t>Putirka (2008) “all three models” combined range</t>
   </si>
   <si>
     <t>Mineral thermobarometry</t>
@@ -870,7 +867,7 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B2" t="b">
         <v>0</v>
@@ -899,7 +896,7 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B3" t="b">
         <v>0</v>
@@ -928,7 +925,7 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B4" t="b">
         <v>0</v>
@@ -957,7 +954,7 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B5" t="b">
         <v>0</v>
@@ -986,7 +983,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B6" t="b">
         <v>0</v>
@@ -1015,7 +1012,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B7" t="b">
         <v>1</v>
@@ -1030,21 +1027,21 @@
         <v>0</v>
       </c>
       <c r="F7" t="s">
-        <v>81</v>
+        <v>1</v>
       </c>
       <c r="G7" t="s">
         <v>68</v>
       </c>
       <c r="I7">
-        <v>1.2</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="J7">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B8" t="b">
         <v>1</v>
@@ -1073,7 +1070,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B9" t="b">
         <v>0</v>
@@ -1108,13 +1105,13 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
+        <v>81</v>
+      </c>
+      <c r="B10" t="b">
+        <v>0</v>
+      </c>
+      <c r="C10" t="s">
         <v>82</v>
-      </c>
-      <c r="B10" t="b">
-        <v>0</v>
-      </c>
-      <c r="C10" t="s">
-        <v>83</v>
       </c>
       <c r="D10">
         <v>2010</v>
@@ -1140,13 +1137,13 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
+        <v>81</v>
+      </c>
+      <c r="B11" t="b">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
         <v>82</v>
-      </c>
-      <c r="B11" t="b">
-        <v>1</v>
-      </c>
-      <c r="C11" t="s">
-        <v>83</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>17</v>
@@ -1172,13 +1169,13 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
+        <v>81</v>
+      </c>
+      <c r="B12" t="b">
+        <v>1</v>
+      </c>
+      <c r="C12" t="s">
         <v>82</v>
-      </c>
-      <c r="B12" t="b">
-        <v>1</v>
-      </c>
-      <c r="C12" t="s">
-        <v>83</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>17</v>
@@ -1204,13 +1201,13 @@
     </row>
     <row r="13" spans="1:15" ht="58" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B13" t="b">
         <v>1</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D13" s="1">
         <v>2006</v>
@@ -1239,13 +1236,13 @@
     </row>
     <row r="14" spans="1:15" ht="58" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B14" t="b">
         <v>1</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D14" s="1">
         <v>2010</v>
@@ -1274,13 +1271,13 @@
     </row>
     <row r="15" spans="1:15" ht="58" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B15" t="b">
         <v>1</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D15" s="1">
         <v>2010</v>
